--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N30_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.04728735570976</v>
+        <v>10.55480815965924</v>
       </c>
       <c r="D2" t="n">
-        <v>36.14534329558907</v>
+        <v>10.65517604512426</v>
       </c>
       <c r="E2" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F2" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.73263564963174</v>
+        <v>36.04728735570976</v>
       </c>
       <c r="D3" t="n">
-        <v>13.89078508570984</v>
+        <v>36.14534329558907</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F3" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.23050189918527</v>
+        <v>13.73263564963174</v>
       </c>
       <c r="D4" t="n">
-        <v>22.1489110252381</v>
+        <v>13.89078508570984</v>
       </c>
       <c r="E4" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F4" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.112398473718081</v>
+        <v>22.23050189918527</v>
       </c>
       <c r="D5" t="n">
-        <v>8.040340543387469</v>
+        <v>22.1489110252381</v>
       </c>
       <c r="E5" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F5" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8830359921783</v>
+        <v>8.112398473718081</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77763370303292</v>
+        <v>8.040340543387469</v>
       </c>
       <c r="E6" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F6" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.776577364794377</v>
+        <v>16.8830359921783</v>
       </c>
       <c r="D7" t="n">
-        <v>6.853603344738461</v>
+        <v>16.77763370303292</v>
       </c>
       <c r="E7" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F7" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.08628280023317</v>
+        <v>6.776577364794377</v>
       </c>
       <c r="D8" t="n">
-        <v>40.96954839294259</v>
+        <v>6.853603344738461</v>
       </c>
       <c r="E8" t="n">
-        <v>11.96751657633619</v>
+        <v>11.62984004831423</v>
       </c>
       <c r="F8" t="n">
-        <v>11.95177787576991</v>
+        <v>11.60700401345413</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,23 +704,55 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
+        <v>41.08628280023317</v>
+      </c>
+      <c r="D9" t="n">
+        <v>40.96954839294259</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11.62984004831423</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.60700401345413</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>W0051F0003T0006Z000C1N30.png</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="n">
         <v>11.3228182696423</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" t="n">
         <v>11.27771932731358</v>
       </c>
-      <c r="E9" t="n">
-        <v>11.96751657633619</v>
-      </c>
-      <c r="F9" t="n">
-        <v>11.95177787576991</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>T1791</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="E10" t="n">
+        <v>11.62984004831423</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11.60700401345413</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.55480815965924</v>
+        <v>1.715156325944627</v>
       </c>
       <c r="D2" t="n">
-        <v>10.65517604512426</v>
+        <v>1.731466107332692</v>
       </c>
       <c r="E2" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F2" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.04728735570976</v>
+        <v>5.857684195302835</v>
       </c>
       <c r="D3" t="n">
-        <v>36.14534329558907</v>
+        <v>5.873618285533224</v>
       </c>
       <c r="E3" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F3" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.73263564963174</v>
+        <v>2.231553293065157</v>
       </c>
       <c r="D4" t="n">
-        <v>13.89078508570984</v>
+        <v>2.25725257642785</v>
       </c>
       <c r="E4" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F4" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.23050189918527</v>
+        <v>3.612456558617607</v>
       </c>
       <c r="D5" t="n">
-        <v>22.1489110252381</v>
+        <v>3.599198041601191</v>
       </c>
       <c r="E5" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F5" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.112398473718081</v>
+        <v>1.318264751979188</v>
       </c>
       <c r="D6" t="n">
-        <v>8.040340543387469</v>
+        <v>1.306555338300464</v>
       </c>
       <c r="E6" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F6" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.8830359921783</v>
+        <v>2.743493348728974</v>
       </c>
       <c r="D7" t="n">
-        <v>16.77763370303292</v>
+        <v>2.72636547674285</v>
       </c>
       <c r="E7" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F7" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.776577364794377</v>
+        <v>1.101193821779086</v>
       </c>
       <c r="D8" t="n">
-        <v>6.853603344738461</v>
+        <v>1.11371054352</v>
       </c>
       <c r="E8" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F8" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.08628280023317</v>
+        <v>6.676520955037891</v>
       </c>
       <c r="D9" t="n">
-        <v>40.96954839294259</v>
+        <v>6.657551613853172</v>
       </c>
       <c r="E9" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F9" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.3228182696423</v>
+        <v>1.839957968816874</v>
       </c>
       <c r="D10" t="n">
-        <v>11.27771932731358</v>
+        <v>1.832629390688457</v>
       </c>
       <c r="E10" t="n">
-        <v>11.62984004831423</v>
+        <v>1.889849007851063</v>
       </c>
       <c r="F10" t="n">
-        <v>11.60700401345413</v>
+        <v>1.886138152186296</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
